--- a/docs/d/55/inyear.xlsx
+++ b/docs/d/55/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 51 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 49 clubs short</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1611,8 +1611,8 @@
       <c r="S9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="9" t="n">
-        <v>0</v>
+      <c r="T9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U9" s="9" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3657,8 +3657,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>0</v>
@@ -5481,8 +5481,8 @@
       <c r="S47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T47" s="9" t="n">
-        <v>0</v>
+      <c r="T47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U47" s="9" t="n">
         <v>0</v>
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6267,13 +6267,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6314,8 +6314,8 @@
       <c r="V55" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W55" s="9" t="n">
-        <v>3</v>
+      <c r="W55" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X55" s="10" t="n">
         <v>4</v>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="P71" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q71" s="9" t="n">
         <v>1</v>
@@ -8184,7 +8184,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8254,8 +8254,8 @@
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -13274,7 +13274,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13439,7 +13439,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -13571,7 +13571,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13604,7 +13604,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -13736,7 +13736,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/docs/d/55/inyear.xlsx
+++ b/docs/d/55/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,11 @@
       <c r="AB8" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1840,7 +1844,11 @@
       <c r="AB11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -3771,7 +3779,11 @@
       <c r="AB30" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC30" s="4" t="inlineStr"/>
+      <c r="AC30" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -4078,7 +4090,11 @@
       <c r="AB33" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -4999,7 +5015,11 @@
       <c r="AB42" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC42" s="4" t="inlineStr"/>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -6946,7 +6966,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7047,7 +7071,11 @@
       <c r="AB62" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC62" s="4" t="inlineStr"/>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -7859,7 +7887,11 @@
       <c r="AB70" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC70" s="4" t="inlineStr"/>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -8667,7 +8699,11 @@
       <c r="AB78" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC78" s="4" t="inlineStr"/>
+      <c r="AC78" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -11725,7 +11761,11 @@
       <c r="AB108" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC108" s="4" t="inlineStr"/>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -12949,7 +12989,11 @@
       <c r="AB120" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC120" s="4" t="inlineStr"/>
+      <c r="AC120" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">

--- a/docs/d/55/inyear.xlsx
+++ b/docs/d/55/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 17 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 49 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 45 clubs short</t>
         </is>
       </c>
     </row>
@@ -2045,8 +2045,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="9" t="n">
         <v>0</v>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2554,8 +2554,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4748,13 +4748,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4795,8 +4795,8 @@
       <c r="V40" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W40" s="9" t="n">
-        <v>3</v>
+      <c r="W40" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X40" s="10" t="n">
         <v>4</v>
@@ -4804,8 +4804,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -5655,7 +5655,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5707,8 +5707,8 @@
       <c r="S49" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T49" s="9" t="n">
-        <v>0</v>
+      <c r="T49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U49" s="9" t="n">
         <v>0</v>
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="P62" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>1</v>
@@ -8381,8 +8381,8 @@
       <c r="W75" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="X75" s="9" t="n">
-        <v>3</v>
+      <c r="X75" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8660,8 +8660,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P78" s="9" t="n">
-        <v>3</v>
+      <c r="P78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q78" s="9" t="n">
         <v>0</v>
@@ -11072,7 +11072,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11142,8 +11142,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -12345,7 +12345,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q114" s="10" t="n">
         <v>2</v>
@@ -13384,7 +13384,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13549,7 +13549,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13615,7 +13615,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13813,7 +13813,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13978,7 +13978,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>

--- a/docs/d/55/inyear.xlsx
+++ b/docs/d/55/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 17 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 45 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 28 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
         <v>0</v>
       </c>
       <c r="S2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U2" s="9" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1124,8 +1124,8 @@
       <c r="Y4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="9" t="n">
-        <v>0</v>
+      <c r="Z4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA4" s="10" t="n">
         <v>1</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2119,8 +2119,8 @@
       <c r="P14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" s="9" t="n">
-        <v>1</v>
+      <c r="Q14" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R14" s="9" t="n">
         <v>0</v>
@@ -2251,8 +2251,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="9" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2453,8 +2453,8 @@
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2857,8 +2857,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -3003,13 +3003,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>4</v>
       </c>
       <c r="W23" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X23" s="9" t="n">
         <v>2</v>
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4703,8 +4703,8 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
@@ -4899,8 +4899,8 @@
       <c r="W41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X41" s="9" t="n">
-        <v>2</v>
+      <c r="X41" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y41" s="9" t="n">
         <v>0</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5286,8 +5286,8 @@
       <c r="P45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" s="9" t="n">
-        <v>1</v>
+      <c r="Q45" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R45" s="9" t="n">
         <v>0</v>
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>0</v>
@@ -5393,8 +5393,8 @@
       <c r="R46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S46" s="9" t="n">
-        <v>0</v>
+      <c r="S46" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T46" s="9" t="n">
         <v>0</v>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="9" t="n">
         <v>0</v>
@@ -7167,8 +7167,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="9" t="n">
         <v>0</v>
@@ -7369,8 +7369,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="9" t="n">
         <v>0</v>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7470,8 +7470,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -7501,7 +7501,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7571,8 +7571,8 @@
       <c r="Y67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z67" s="9" t="n">
-        <v>0</v>
+      <c r="Z67" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA67" s="10" t="n">
         <v>1</v>
@@ -8084,8 +8084,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="9" t="n">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8972,7 +8972,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9922,8 +9922,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10124,8 +10124,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -10668,7 +10668,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10738,8 +10738,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -10870,7 +10870,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10940,8 +10940,8 @@
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
@@ -11128,7 +11128,7 @@
         <v>1</v>
       </c>
       <c r="U102" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V102" s="9" t="n">
         <v>1</v>
@@ -11173,7 +11173,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11243,8 +11243,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -11906,13 +11906,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11962,8 +11962,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="9" t="n">
         <v>0</v>
@@ -12304,7 +12304,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12353,8 +12353,8 @@
       <c r="R114" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S114" s="9" t="n">
-        <v>1</v>
+      <c r="S114" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T114" s="9" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q117" s="9" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13186,8 +13186,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -13285,7 +13285,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -13351,7 +13351,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13384,7 +13384,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13549,7 +13549,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13582,7 +13582,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13714,7 +13714,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13747,7 +13747,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13945,7 +13945,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13978,7 +13978,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14077,7 +14077,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -14110,7 +14110,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/55/inyear.xlsx
+++ b/docs/d/55/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 17 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 28 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 28 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1068,17 +1068,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="8" t="n">
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1270,17 +1270,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="8" t="n">
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1472,13 +1472,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="P8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="9" t="n">
         <v>1</v>
@@ -1507,8 +1507,8 @@
       <c r="R8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="9" t="n">
-        <v>1</v>
+      <c r="S8" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T8" s="9" t="n">
         <v>0</v>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>2</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="9" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -1826,8 +1826,8 @@
       <c r="V11" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W11" s="9" t="n">
-        <v>2</v>
+      <c r="W11" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X11" s="10" t="n">
         <v>7</v>
@@ -1884,17 +1884,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1989,17 +1989,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M13" s="8" t="n">
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2090,17 +2090,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="8" t="n">
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2296,13 +2296,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2397,13 +2397,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2643,11 +2643,11 @@
       <c r="U19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="9" t="n">
-        <v>0</v>
+      <c r="V19" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X19" s="9" t="n">
         <v>0</v>
@@ -2700,17 +2700,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M20" s="8" t="n">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2845,8 +2845,8 @@
       <c r="U21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="9" t="n">
-        <v>2</v>
+      <c r="V21" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2902,17 +2902,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="8" t="n">
@@ -2947,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3003,13 +3003,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>4</v>
       </c>
       <c r="W23" s="10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="X23" s="9" t="n">
         <v>2</v>
@@ -3102,13 +3102,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3302,13 +3302,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3403,17 +3403,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3508,13 +3508,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3609,13 +3609,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3714,17 +3714,17 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M30" s="8" t="n">
@@ -3758,8 +3758,8 @@
       <c r="U30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V30" s="9" t="n">
-        <v>1</v>
+      <c r="V30" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3819,17 +3819,17 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M31" s="8" t="n">
@@ -3920,13 +3920,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -4025,13 +4025,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4130,13 +4130,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4235,17 +4235,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="8" t="n">
@@ -4340,13 +4340,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4441,13 +4441,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4542,17 +4542,17 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M38" s="8" t="n">
@@ -4647,13 +4647,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4748,13 +4748,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4950,13 +4950,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5156,13 +5156,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-4</v>
+        <v>-21</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5257,13 +5257,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5358,17 +5358,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5463,13 +5463,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>0</v>
       </c>
       <c r="S47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" s="10" t="n">
         <v>1</v>
@@ -5564,17 +5564,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="8" t="n">
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5774,13 +5774,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5875,13 +5875,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5980,17 +5980,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="P52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" s="9" t="n">
         <v>0</v>
@@ -6085,17 +6085,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M53" s="8" t="n">
@@ -6133,7 +6133,7 @@
         <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X53" s="10" t="n">
         <v>5</v>
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6186,13 +6186,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6230,8 +6230,8 @@
       <c r="U54" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V54" s="9" t="n">
-        <v>3</v>
+      <c r="V54" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -6287,13 +6287,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>4</v>
       </c>
       <c r="W55" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X55" s="10" t="n">
         <v>4</v>
@@ -6392,13 +6392,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6598,13 +6598,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6699,17 +6699,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6800,13 +6800,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6901,13 +6901,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6948,8 +6948,8 @@
       <c r="V61" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W61" s="9" t="n">
-        <v>1</v>
+      <c r="W61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>7</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7006,13 +7006,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>99</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="P62" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>1</v>
@@ -7050,11 +7050,11 @@
       <c r="U62" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" s="9" t="n">
-        <v>0</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W62" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>7</v>
@@ -7111,13 +7111,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7212,13 +7212,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7313,13 +7313,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7414,13 +7414,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7515,13 +7515,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7550,8 +7550,8 @@
       <c r="R67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S67" s="9" t="n">
-        <v>1</v>
+      <c r="S67" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T67" s="10" t="n">
         <v>1</v>
@@ -7616,13 +7616,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7822,13 +7822,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>1</v>
@@ -7860,14 +7860,14 @@
       <c r="S70" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T70" s="9" t="n">
-        <v>0</v>
+      <c r="T70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8129,13 +8129,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8274,8 +8274,8 @@
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="9" t="n">
-        <v>3</v>
+      <c r="V74" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8331,17 +8331,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8379,7 +8379,7 @@
         <v>4</v>
       </c>
       <c r="W75" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X75" s="10" t="n">
         <v>4</v>
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8432,13 +8432,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8476,8 +8476,8 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>3</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8739,13 +8739,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8840,13 +8840,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8887,8 +8887,8 @@
       <c r="V80" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W80" s="9" t="n">
-        <v>3</v>
+      <c r="W80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>5</v>
@@ -8945,13 +8945,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>4</v>
       </c>
       <c r="W81" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X81" s="10" t="n">
         <v>5</v>
@@ -9050,13 +9050,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9151,13 +9151,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9454,13 +9454,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9559,13 +9559,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9664,17 +9664,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="8" t="n">
@@ -9765,13 +9765,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9866,13 +9866,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9967,13 +9967,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10068,13 +10068,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10169,13 +10169,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>5</v>
+        <v>-9</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -10274,13 +10274,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-7</v>
+        <v>-13</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10375,13 +10375,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -10476,13 +10476,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10577,13 +10577,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>4</v>
       </c>
       <c r="W97" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X97" s="9" t="n">
         <v>3</v>
@@ -10668,7 +10668,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10682,13 +10682,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10726,11 +10726,11 @@
       <c r="U98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W98" s="9" t="n">
-        <v>0</v>
+      <c r="V98" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W98" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="X98" s="9" t="n">
         <v>3</v>
@@ -10783,13 +10783,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10884,13 +10884,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10985,13 +10985,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11086,13 +11086,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>2</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11187,13 +11187,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11288,13 +11288,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11490,13 +11490,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11595,13 +11595,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11743,8 +11743,8 @@
       <c r="V108" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W108" s="9" t="n">
-        <v>1</v>
+      <c r="W108" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X108" s="9" t="n">
         <v>2</v>
@@ -11801,13 +11801,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>3</v>
+        <v>-14</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11906,13 +11906,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -12007,17 +12007,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12112,13 +12112,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12217,13 +12217,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>1</v>
@@ -12255,11 +12255,11 @@
       <c r="S113" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U113" s="9" t="n">
-        <v>0</v>
+      <c r="T113" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V113" s="9" t="n">
         <v>0</v>
@@ -12318,17 +12318,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M114" s="8" t="n">
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12423,13 +12423,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12461,8 +12461,8 @@
       <c r="S115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T115" s="9" t="n">
-        <v>0</v>
+      <c r="T115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U115" s="9" t="n">
         <v>0</v>
@@ -12522,13 +12522,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12623,13 +12623,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12667,8 +12667,8 @@
       <c r="U117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V117" s="9" t="n">
-        <v>2</v>
+      <c r="V117" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12722,17 +12722,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12823,13 +12823,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12924,17 +12924,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="8" t="n">
@@ -12954,7 +12954,7 @@
         <v>2</v>
       </c>
       <c r="Q120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" s="9" t="n">
         <v>0</v>
@@ -12972,7 +12972,7 @@
         <v>4</v>
       </c>
       <c r="W120" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>5</v>
@@ -13029,13 +13029,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13130,13 +13130,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -13318,7 +13318,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13351,7 +13351,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13366,7 +13366,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -13384,7 +13384,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13432,7 +13432,7 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -13483,7 +13483,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -13498,7 +13498,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -13531,7 +13531,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -13564,7 +13564,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -13597,7 +13597,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -13648,7 +13648,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -13663,7 +13663,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -13681,13 +13681,13 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -13696,7 +13696,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -13714,13 +13714,13 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -13747,7 +13747,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13780,7 +13780,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13795,7 +13795,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -13813,7 +13813,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13894,7 +13894,7 @@
         <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -13945,7 +13945,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14011,13 +14011,13 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -14044,7 +14044,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -14059,7 +14059,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -14077,7 +14077,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -14092,7 +14092,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -14125,7 +14125,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/55/inyear.xlsx
+++ b/docs/d/55/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/55/inyear.xlsx
+++ b/docs/d/55/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/55/inyear.xlsx
+++ b/docs/d/55/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/55/inyear.xlsx
+++ b/docs/d/55/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/55/inyear.xlsx
+++ b/docs/d/55/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 17 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 28 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 28 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1472,13 +1472,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2902,13 +2902,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -3302,13 +3302,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3609,13 +3609,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3714,17 +3714,17 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M30" s="8" t="n">
@@ -3819,13 +3819,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3920,13 +3920,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4130,13 +4130,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4235,17 +4235,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M35" s="8" t="n">
@@ -4279,8 +4279,8 @@
       <c r="U35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="9" t="n">
-        <v>3</v>
+      <c r="V35" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4468,7 +4468,7 @@
         </is>
       </c>
       <c r="P37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="9" t="n">
         <v>0</v>
@@ -4936,7 +4936,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4950,13 +4950,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -4979,14 +4979,14 @@
       <c r="P42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" s="9" t="n">
-        <v>0</v>
+      <c r="Q42" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S42" s="9" t="n">
-        <v>0</v>
+      <c r="S42" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T42" s="10" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="P49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" s="9" t="n">
         <v>1</v>
@@ -6085,13 +6085,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6901,13 +6901,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>4</v>
       </c>
       <c r="W61" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>7</v>
@@ -7006,13 +7006,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>99</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="P62" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>1</v>
@@ -7054,7 +7054,7 @@
         <v>4</v>
       </c>
       <c r="W62" s="10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>7</v>
@@ -7501,7 +7501,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7556,8 +7556,8 @@
       <c r="T67" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U67" s="9" t="n">
-        <v>0</v>
+      <c r="U67" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V67" s="9" t="n">
         <v>2</v>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q69" s="9" t="n">
         <v>1</v>
@@ -7808,7 +7808,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7857,8 +7857,8 @@
       <c r="R70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S70" s="9" t="n">
-        <v>1</v>
+      <c r="S70" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T70" s="10" t="n">
         <v>1</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>4</v>
       </c>
       <c r="W74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X74" s="9" t="n">
         <v>1</v>
@@ -8331,17 +8331,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L75" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8840,13 +8840,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" s="10" t="n">
         <v>2</v>
@@ -9559,13 +9559,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -10068,13 +10068,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10274,13 +10274,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10375,13 +10375,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -11187,13 +11187,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
         <v>0</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
@@ -11787,7 +11787,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11801,13 +11801,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11845,8 +11845,8 @@
       <c r="U109" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V109" s="9" t="n">
-        <v>3</v>
+      <c r="V109" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11906,13 +11906,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -12007,13 +12007,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
@@ -12217,13 +12217,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>1</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12522,13 +12522,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12623,13 +12623,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>4</v>
       </c>
       <c r="W117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X117" s="10" t="n">
         <v>6</v>
@@ -12722,13 +12722,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -13516,7 +13516,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13531,7 +13531,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -13582,7 +13582,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13747,7 +13747,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13795,7 +13795,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -14011,7 +14011,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>

--- a/docs/d/55/inyear.xlsx
+++ b/docs/d/55/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 17 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 28 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 28 clubs short</t>
         </is>
       </c>
     </row>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1817,8 +1817,8 @@
       <c r="S11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="9" t="n">
-        <v>0</v>
+      <c r="T11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U11" s="9" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="9" t="n">
         <v>0</v>
@@ -1922,8 +1922,8 @@
       <c r="S12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T12" s="9" t="n">
-        <v>0</v>
+      <c r="T12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U12" s="9" t="n">
         <v>0</v>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2296,13 +2296,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2340,11 +2340,11 @@
       <c r="U16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="9" t="n">
-        <v>3</v>
+      <c r="V16" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>4</v>
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2902,13 +2902,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -3102,13 +3102,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3403,17 +3403,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3448,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3920,13 +3920,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4025,13 +4025,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4069,8 +4069,8 @@
       <c r="U33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="9" t="n">
-        <v>3</v>
+      <c r="V33" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4264,8 +4264,8 @@
       <c r="P35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="9" t="n">
-        <v>0</v>
+      <c r="Q35" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>0</v>
@@ -4542,17 +4542,17 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L38" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-8</v>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M38" s="8" t="n">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -5774,13 +5774,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -6085,13 +6085,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X53" s="10" t="n">
         <v>5</v>
@@ -6186,13 +6186,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>4</v>
       </c>
       <c r="W54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X54" s="10" t="n">
         <v>4</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7006,13 +7006,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>99</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-20</v>
+        <v>-16</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7033,28 +7033,28 @@
         </is>
       </c>
       <c r="P62" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q62" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="Q62" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="S62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="T62" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U62" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V62" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W62" s="10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>7</v>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>1</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8331,13 +8331,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8369,8 +8369,8 @@
       <c r="S75" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T75" s="9" t="n">
-        <v>0</v>
+      <c r="T75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U75" s="9" t="n">
         <v>0</v>
@@ -8378,8 +8378,8 @@
       <c r="V75" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W75" s="9" t="n">
-        <v>3</v>
+      <c r="W75" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X75" s="10" t="n">
         <v>4</v>
@@ -8840,13 +8840,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80" s="9" t="n">
         <v>0</v>
@@ -8975,7 +8975,7 @@
         <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>0</v>
@@ -9765,13 +9765,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9967,13 +9967,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10068,13 +10068,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -11086,13 +11086,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11187,13 +11187,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11801,13 +11801,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>4</v>
       </c>
       <c r="W109" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X109" s="10" t="n">
         <v>6</v>
@@ -11906,13 +11906,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -12217,13 +12217,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12962,8 +12962,8 @@
       <c r="S120" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T120" s="9" t="n">
-        <v>0</v>
+      <c r="T120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U120" s="9" t="n">
         <v>0</v>
@@ -13130,13 +13130,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>1</v>
       </c>
       <c r="Q122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
@@ -13351,7 +13351,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13384,7 +13384,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13498,7 +13498,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -13516,7 +13516,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -13714,7 +13714,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -13780,7 +13780,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14110,7 +14110,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
